--- a/input/DummyFrench.xlsx
+++ b/input/DummyFrench.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coltinternal-my.sharepoint.com/personal/rjha1_internal_colt_net/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coltinternal-my.sharepoint.com/personal/rjha1_internal_colt_net/Documents/Desktop/TranslateToEnglish/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E7AB2E0-1915-4A75-A245-775879F46D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{2E7AB2E0-1915-4A75-A245-775879F46D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AE21DFB-0D27-4115-B645-B5EE0B5DA053}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1ADB8C42-4624-4BA6-B5B3-BF6F8A69C8B6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="58">
   <si>
     <t>Zones éligibles à la fibre optique pour les abonnés — Saitama</t>
   </si>
@@ -280,12 +280,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -313,10 +313,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654E54C9-3CBB-44CD-9D5B-38123E12106F}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.81640625" customWidth="1"/>
@@ -664,52 +660,70 @@
     <col min="7" max="7" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+    </row>
+    <row r="2" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="4" spans="1:21" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -719,15 +733,15 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2"/>
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -737,15 +751,15 @@
       <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="2"/>
       <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -755,15 +769,15 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2"/>
       <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -773,15 +787,15 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="2"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -791,15 +805,15 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -809,15 +823,15 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2"/>
       <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -827,15 +841,15 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2"/>
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -845,15 +859,15 @@
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2"/>
       <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -863,15 +877,15 @@
       <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="2"/>
       <c r="E13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -881,15 +895,15 @@
       <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="2"/>
       <c r="E14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -899,15 +913,15 @@
       <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="2"/>
       <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -917,11 +931,11 @@
       <c r="C16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -935,11 +949,11 @@
       <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="2"/>
       <c r="E17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -953,11 +967,11 @@
       <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="2"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -971,13 +985,13 @@
       <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -991,13 +1005,13 @@
       <c r="C20" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1011,13 +1025,13 @@
       <c r="C21" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1031,11 +1045,11 @@
       <c r="C22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="2"/>
       <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1049,11 +1063,11 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="2"/>
       <c r="E23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1067,11 +1081,11 @@
       <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="2"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1085,11 +1099,11 @@
       <c r="C25" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="2"/>
       <c r="E25" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1103,11 +1117,11 @@
       <c r="C26" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="2"/>
       <c r="E26" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1121,11 +1135,11 @@
       <c r="C27" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="2"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1139,11 +1153,11 @@
       <c r="C28" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="2"/>
       <c r="E28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1157,11 +1171,11 @@
       <c r="C29" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="2"/>
       <c r="E29" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1175,11 +1189,11 @@
       <c r="C30" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="2"/>
       <c r="E30" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1193,11 +1207,11 @@
       <c r="C31" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="2"/>
       <c r="E31" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1211,11 +1225,11 @@
       <c r="C32" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="2"/>
       <c r="E32" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1229,11 +1243,11 @@
       <c r="C33" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="2"/>
       <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1247,13 +1261,13 @@
       <c r="C34" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1267,13 +1281,13 @@
       <c r="C35" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1287,11 +1301,11 @@
       <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="2"/>
       <c r="E36" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1305,11 +1319,11 @@
       <c r="C37" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="4"/>
+      <c r="D37" s="2"/>
       <c r="E37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1323,13 +1337,13 @@
       <c r="C38" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1343,13 +1357,13 @@
       <c r="C39" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E39" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1363,13 +1377,13 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E40" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G40" t="s">
@@ -1386,13 +1400,13 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E41" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G41" t="s">
@@ -1409,13 +1423,13 @@
       <c r="C42" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G42" t="s">
@@ -1432,13 +1446,13 @@
       <c r="C43" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E43" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G43" t="s">
@@ -1455,13 +1469,13 @@
       <c r="C44" t="s">
         <v>52</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1475,13 +1489,13 @@
       <c r="C45" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1495,13 +1509,13 @@
       <c r="C46" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E46" t="s">
         <v>38</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1515,11 +1529,11 @@
       <c r="C47" t="s">
         <v>54</v>
       </c>
-      <c r="D47" s="4"/>
+      <c r="D47" s="2"/>
       <c r="E47" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1533,13 +1547,13 @@
       <c r="C48" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E48" t="s">
         <v>38</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1553,11 +1567,11 @@
       <c r="C49" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="4"/>
+      <c r="D49" s="2"/>
       <c r="E49" t="s">
         <v>38</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1571,11 +1585,11 @@
       <c r="C50" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="4"/>
+      <c r="D50" s="2"/>
       <c r="E50" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1589,20 +1603,22 @@
       <c r="C51" t="s">
         <v>57</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E51" t="s">
         <v>38</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="2" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H1:N1"/>
+    <mergeCell ref="O1:U1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
